--- a/data/book_record.xlsx
+++ b/data/book_record.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="470">
   <si>
     <t>title</t>
   </si>
@@ -1415,6 +1415,12 @@
   </si>
   <si>
     <t>Makana Yamamoto</t>
+  </si>
+  <si>
+    <t>Animal Farm</t>
+  </si>
+  <si>
+    <t>George Orwell</t>
   </si>
 </sst>
 </file>
@@ -2625,7 +2631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J204"/>
+  <dimension ref="A1:J205"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="51.1562" style="1" customWidth="1"/>
@@ -8842,6 +8848,36 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="205" ht="13.55" customHeight="1">
+      <c r="A205" t="s" s="5">
+        <v>468</v>
+      </c>
+      <c r="B205" t="s" s="5">
+        <v>469</v>
+      </c>
+      <c r="C205" t="s" s="5">
+        <v>12</v>
+      </c>
+      <c r="D205" t="s" s="5">
+        <v>279</v>
+      </c>
+      <c r="E205" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F205" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G205" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="H205" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I205" s="7"/>
+      <c r="J205" s="6">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>

--- a/data/book_record.xlsx
+++ b/data/book_record.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="478">
   <si>
     <t>title</t>
   </si>
@@ -1421,6 +1421,30 @@
   </si>
   <si>
     <t>George Orwell</t>
+  </si>
+  <si>
+    <t>The Hitchhiker's Guide to the Galaxy</t>
+  </si>
+  <si>
+    <t>Douglas Adams</t>
+  </si>
+  <si>
+    <t>To Say Nothing of the Dog</t>
+  </si>
+  <si>
+    <t>Connie Willis</t>
+  </si>
+  <si>
+    <t>Synners</t>
+  </si>
+  <si>
+    <t>Pat Cadigan</t>
+  </si>
+  <si>
+    <t>Jitterbug</t>
+  </si>
+  <si>
+    <t>Gareth L. Powell</t>
   </si>
 </sst>
 </file>
@@ -2631,7 +2655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J205"/>
+  <dimension ref="A1:J209"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="51.1562" style="1" customWidth="1"/>
@@ -8859,7 +8883,7 @@
         <v>12</v>
       </c>
       <c r="D205" t="s" s="5">
-        <v>279</v>
+        <v>364</v>
       </c>
       <c r="E205" t="s" s="5">
         <v>14</v>
@@ -8875,6 +8899,126 @@
       </c>
       <c r="I205" s="7"/>
       <c r="J205" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="206" ht="13.55" customHeight="1">
+      <c r="A206" t="s" s="5">
+        <v>470</v>
+      </c>
+      <c r="B206" t="s" s="5">
+        <v>471</v>
+      </c>
+      <c r="C206" t="s" s="5">
+        <v>12</v>
+      </c>
+      <c r="D206" t="s" s="5">
+        <v>364</v>
+      </c>
+      <c r="E206" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F206" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G206" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="H206" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I206" s="7"/>
+      <c r="J206" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="207" ht="13.55" customHeight="1">
+      <c r="A207" t="s" s="5">
+        <v>472</v>
+      </c>
+      <c r="B207" t="s" s="5">
+        <v>473</v>
+      </c>
+      <c r="C207" t="s" s="5">
+        <v>12</v>
+      </c>
+      <c r="D207" t="s" s="5">
+        <v>279</v>
+      </c>
+      <c r="E207" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F207" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G207" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="H207" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I207" s="7"/>
+      <c r="J207" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="208" ht="13.55" customHeight="1">
+      <c r="A208" t="s" s="5">
+        <v>474</v>
+      </c>
+      <c r="B208" t="s" s="5">
+        <v>475</v>
+      </c>
+      <c r="C208" t="s" s="5">
+        <v>109</v>
+      </c>
+      <c r="D208" t="s" s="5">
+        <v>71</v>
+      </c>
+      <c r="E208" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F208" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G208" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="H208" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I208" s="7"/>
+      <c r="J208" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="209" ht="13.55" customHeight="1">
+      <c r="A209" t="s" s="5">
+        <v>476</v>
+      </c>
+      <c r="B209" t="s" s="5">
+        <v>477</v>
+      </c>
+      <c r="C209" t="s" s="5">
+        <v>12</v>
+      </c>
+      <c r="D209" t="s" s="5">
+        <v>71</v>
+      </c>
+      <c r="E209" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F209" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G209" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="H209" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I209" s="7"/>
+      <c r="J209" s="6">
         <v>2026</v>
       </c>
     </row>

--- a/data/book_record.xlsx
+++ b/data/book_record.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="515">
   <si>
     <t>title</t>
   </si>
@@ -124,7 +124,7 @@
     <t>Greece</t>
   </si>
   <si>
-    <t>Classic, Philosophy</t>
+    <t>Classics, Philosophy</t>
   </si>
   <si>
     <t>Ancient Greek</t>
@@ -154,7 +154,7 @@
     <t>Harper Lee</t>
   </si>
   <si>
-    <t>Classic</t>
+    <t>Classics, Literary Fiction</t>
   </si>
   <si>
     <t>Fiction</t>
@@ -250,7 +250,7 @@
     <t>William Golding</t>
   </si>
   <si>
-    <t>Classic, Young Adult</t>
+    <t>Classics, Young Adult, Literary Fiction</t>
   </si>
   <si>
     <t>King Lear</t>
@@ -259,6 +259,9 @@
     <t>William Shakespeare</t>
   </si>
   <si>
+    <t>Classics</t>
+  </si>
+  <si>
     <t>The Spirit of the Chinese People</t>
   </si>
   <si>
@@ -289,6 +292,9 @@
     <t>Norway</t>
   </si>
   <si>
+    <t>Philosophy, History, Literary Fiction</t>
+  </si>
+  <si>
     <t>Norwegian</t>
   </si>
   <si>
@@ -565,7 +571,7 @@
     <t>Johann Wolfgang von Goethe</t>
   </si>
   <si>
-    <t>Classic, Poetry</t>
+    <t>Classics, Poetry</t>
   </si>
   <si>
     <t>Emergence: From Chaos to Order</t>
@@ -838,7 +844,7 @@
     <t>David J. Griffiths</t>
   </si>
   <si>
-    <t>Classical Mechanics</t>
+    <t>Classicsal Mechanics</t>
   </si>
   <si>
     <t>John R. Taylor</t>
@@ -931,39 +937,42 @@
     <t>Afghanistan, United States</t>
   </si>
   <si>
+    <t>Historical Fiction, Literary Fiction</t>
+  </si>
+  <si>
+    <t>Putin Country: A Journey into the Real Russia</t>
+  </si>
+  <si>
+    <t>Anne Garrels</t>
+  </si>
+  <si>
+    <t>The Technological Singularity</t>
+  </si>
+  <si>
+    <t>Murray Shanahan</t>
+  </si>
+  <si>
+    <t>Gödel's Proof, Revised Edition</t>
+  </si>
+  <si>
+    <t>Ernest Nagel, James R. Newman, Douglas R. Hofstadter</t>
+  </si>
+  <si>
+    <t>Slovakia, United States, United States, United States</t>
+  </si>
+  <si>
+    <t>Ball Lightning</t>
+  </si>
+  <si>
+    <t>Fences</t>
+  </si>
+  <si>
+    <t>August Wilson</t>
+  </si>
+  <si>
     <t>Historical Fiction</t>
   </si>
   <si>
-    <t>Putin Country: A Journey into the Real Russia</t>
-  </si>
-  <si>
-    <t>Anne Garrels</t>
-  </si>
-  <si>
-    <t>The Technological Singularity</t>
-  </si>
-  <si>
-    <t>Murray Shanahan</t>
-  </si>
-  <si>
-    <t>Gödel's Proof, Revised Edition</t>
-  </si>
-  <si>
-    <t>Ernest Nagel, James R. Newman, Douglas R. Hofstadter</t>
-  </si>
-  <si>
-    <t>Slovakia, United States, United States, United States</t>
-  </si>
-  <si>
-    <t>Ball Lightning</t>
-  </si>
-  <si>
-    <t>Fences</t>
-  </si>
-  <si>
-    <t>August Wilson</t>
-  </si>
-  <si>
     <t>Blindsight</t>
   </si>
   <si>
@@ -1003,7 +1012,7 @@
     <t>Supernova Era</t>
   </si>
   <si>
-    <t>The Wandering Earth: Classic Science Fiction Collection</t>
+    <t>The Wandering Earth: Classics Science Fiction Collection</t>
   </si>
   <si>
     <t>Galaxy Formation and Evolution</t>
@@ -1090,7 +1099,7 @@
     <t>Rendezvous with Rama</t>
   </si>
   <si>
-    <t>Classic, Science Fiction</t>
+    <t>Classics, Science Fiction</t>
   </si>
   <si>
     <t>The Fountains of Paradise</t>
@@ -1105,7 +1114,7 @@
     <t>Ursula K. Le Guin</t>
   </si>
   <si>
-    <t>Classic, Science Fiction, Speculative Fiction</t>
+    <t>Classics, Science Fiction, Speculative Fiction</t>
   </si>
   <si>
     <t>The Dispossessed</t>
@@ -1282,6 +1291,9 @@
     <t>Mary Shelley</t>
   </si>
   <si>
+    <t>Classics, Science Fiction, Speculative Fiction, Literary Fiction</t>
+  </si>
+  <si>
     <t>Hard to Be a God</t>
   </si>
   <si>
@@ -1445,6 +1457,105 @@
   </si>
   <si>
     <t>Gareth L. Powell</t>
+  </si>
+  <si>
+    <t>The Employees</t>
+  </si>
+  <si>
+    <t>Olga Ravn</t>
+  </si>
+  <si>
+    <t>Science Fiction, Speculative Fiction, Literary Fiction</t>
+  </si>
+  <si>
+    <t>Toward Eternity</t>
+  </si>
+  <si>
+    <t>Anton Hur</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>The Algebraist</t>
+  </si>
+  <si>
+    <t>Ian M. Banks</t>
+  </si>
+  <si>
+    <t>Orbital</t>
+  </si>
+  <si>
+    <t>Samantha Harvey</t>
+  </si>
+  <si>
+    <t>Science Fiction, Literary Fiction</t>
+  </si>
+  <si>
+    <t>The Metamorphosis of Prime Intellect</t>
+  </si>
+  <si>
+    <t>Roger Williams</t>
+  </si>
+  <si>
+    <t>There Is No Antimemetics Division</t>
+  </si>
+  <si>
+    <t>qntm</t>
+  </si>
+  <si>
+    <t>I Who Have Never Known Men</t>
+  </si>
+  <si>
+    <t>Jacqueline Harpman</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Speculative Fiction, Literary Fiction</t>
+  </si>
+  <si>
+    <t>The Library of Babel</t>
+  </si>
+  <si>
+    <t>Jorge Luis Borges</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Speculative Fiction, Classics, Philosophy</t>
+  </si>
+  <si>
+    <t>Bhagavad Gita</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Philosophy, Religion, Classics</t>
+  </si>
+  <si>
+    <t>Sanskrit</t>
+  </si>
+  <si>
+    <t>The Proposal</t>
+  </si>
+  <si>
+    <t>Bae Myung-hoon</t>
+  </si>
+  <si>
+    <t>Korean</t>
+  </si>
+  <si>
+    <t>Every Version of You</t>
+  </si>
+  <si>
+    <t>Grace Chan</t>
+  </si>
+  <si>
+    <t>Malaysia, Australia</t>
   </si>
 </sst>
 </file>
@@ -2655,13 +2766,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J209"/>
+  <dimension ref="A1:J221"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="51.1562" style="1" customWidth="1"/>
+    <col min="1" max="1" width="47.9688" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.5312" style="1" customWidth="1"/>
     <col min="3" max="3" width="26.4141" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6719" style="1" customWidth="1"/>
+    <col min="4" max="4" width="38.8516" style="1" customWidth="1"/>
     <col min="5" max="6" width="8.85156" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.6719" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.3516" style="1" customWidth="1"/>
@@ -3441,7 +3552,7 @@
         <v>12</v>
       </c>
       <c r="D26" t="s" s="5">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="E26" t="s" s="5">
         <v>14</v>
@@ -3462,13 +3573,13 @@
     </row>
     <row r="27" ht="13.55" customHeight="1">
       <c r="A27" t="s" s="5">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B27" t="s" s="5">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s" s="5">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s" s="5">
         <v>21</v>
@@ -3492,7 +3603,7 @@
     </row>
     <row r="28" ht="13.55" customHeight="1">
       <c r="A28" t="s" s="5">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s" s="5">
         <v>81</v>
@@ -3501,7 +3612,7 @@
         <v>12</v>
       </c>
       <c r="D28" t="s" s="5">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="E28" t="s" s="5">
         <v>14</v>
@@ -3522,13 +3633,13 @@
     </row>
     <row r="29" ht="13.55" customHeight="1">
       <c r="A29" t="s" s="5">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B29" t="s" s="5">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s" s="5">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s" s="5">
         <v>31</v>
@@ -3552,16 +3663,16 @@
     </row>
     <row r="30" ht="13.55" customHeight="1">
       <c r="A30" t="s" s="5">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B30" t="s" s="5">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s" s="5">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s" s="5">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="E30" t="s" s="5">
         <v>14</v>
@@ -3570,7 +3681,7 @@
         <v>48</v>
       </c>
       <c r="G30" t="s" s="5">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H30" t="s" s="5">
         <v>17</v>
@@ -3584,13 +3695,13 @@
     </row>
     <row r="31" ht="13.55" customHeight="1">
       <c r="A31" t="s" s="5">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B31" t="s" s="5">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s" s="5">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D31" t="s" s="5">
         <v>31</v>
@@ -3614,13 +3725,13 @@
     </row>
     <row r="32" ht="13.55" customHeight="1">
       <c r="A32" t="s" s="5">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B32" t="s" s="5">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s" s="5">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s" s="5">
         <v>31</v>
@@ -3632,7 +3743,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s" s="5">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H32" t="s" s="5">
         <v>17</v>
@@ -3644,13 +3755,13 @@
     </row>
     <row r="33" ht="13.55" customHeight="1">
       <c r="A33" t="s" s="5">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B33" t="s" s="5">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s" s="5">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D33" t="s" s="5">
         <v>31</v>
@@ -3674,10 +3785,10 @@
     </row>
     <row r="34" ht="13.55" customHeight="1">
       <c r="A34" t="s" s="5">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B34" t="s" s="5">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C34" t="s" s="5">
         <v>20</v>
@@ -3704,16 +3815,16 @@
     </row>
     <row r="35" ht="13.55" customHeight="1">
       <c r="A35" t="s" s="5">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s" s="5">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s" s="5">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D35" t="s" s="5">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E35" t="s" s="5">
         <v>14</v>
@@ -3734,13 +3845,13 @@
     </row>
     <row r="36" ht="13.55" customHeight="1">
       <c r="A36" t="s" s="5">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B36" t="s" s="5">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C36" t="s" s="5">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D36" t="s" s="5">
         <v>56</v>
@@ -3764,10 +3875,10 @@
     </row>
     <row r="37" ht="13.55" customHeight="1">
       <c r="A37" t="s" s="5">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B37" t="s" s="5">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C37" t="s" s="5">
         <v>12</v>
@@ -3794,10 +3905,10 @@
     </row>
     <row r="38" ht="13.55" customHeight="1">
       <c r="A38" t="s" s="5">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B38" t="s" s="5">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C38" t="s" s="5">
         <v>12</v>
@@ -3824,13 +3935,13 @@
     </row>
     <row r="39" ht="13.55" customHeight="1">
       <c r="A39" t="s" s="5">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B39" t="s" s="5">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C39" t="s" s="5">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D39" t="s" s="5">
         <v>31</v>
@@ -3854,13 +3965,13 @@
     </row>
     <row r="40" ht="13.55" customHeight="1">
       <c r="A40" t="s" s="5">
+        <v>119</v>
+      </c>
+      <c r="B40" t="s" s="5">
         <v>117</v>
       </c>
-      <c r="B40" t="s" s="5">
-        <v>115</v>
-      </c>
       <c r="C40" t="s" s="5">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D40" t="s" s="5">
         <v>31</v>
@@ -3884,13 +3995,13 @@
     </row>
     <row r="41" ht="13.55" customHeight="1">
       <c r="A41" t="s" s="5">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B41" t="s" s="5">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C41" t="s" s="5">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D41" t="s" s="5">
         <v>31</v>
@@ -3914,10 +4025,10 @@
     </row>
     <row r="42" ht="13.55" customHeight="1">
       <c r="A42" t="s" s="5">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B42" t="s" s="5">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C42" t="s" s="5">
         <v>12</v>
@@ -3944,7 +4055,7 @@
     </row>
     <row r="43" ht="13.55" customHeight="1">
       <c r="A43" t="s" s="5">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B43" t="s" s="5">
         <v>58</v>
@@ -3976,13 +4087,13 @@
     </row>
     <row r="44" ht="13.55" customHeight="1">
       <c r="A44" t="s" s="5">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B44" t="s" s="5">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C44" t="s" s="5">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D44" t="s" s="5">
         <v>31</v>
@@ -4006,10 +4117,10 @@
     </row>
     <row r="45" ht="13.55" customHeight="1">
       <c r="A45" t="s" s="5">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B45" t="s" s="5">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C45" t="s" s="5">
         <v>30</v>
@@ -4036,10 +4147,10 @@
     </row>
     <row r="46" ht="13.55" customHeight="1">
       <c r="A46" t="s" s="5">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B46" t="s" s="5">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C46" t="s" s="5">
         <v>30</v>
@@ -4066,13 +4177,13 @@
     </row>
     <row r="47" ht="13.55" customHeight="1">
       <c r="A47" t="s" s="5">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B47" t="s" s="5">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C47" t="s" s="5">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D47" t="s" s="5">
         <v>31</v>
@@ -4084,7 +4195,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s" s="5">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H47" t="s" s="5">
         <v>17</v>
@@ -4096,16 +4207,16 @@
     </row>
     <row r="48" ht="13.55" customHeight="1">
       <c r="A48" t="s" s="5">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B48" t="s" s="5">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C48" t="s" s="5">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D48" t="s" s="5">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E48" t="s" s="5">
         <v>27</v>
@@ -4126,10 +4237,10 @@
     </row>
     <row r="49" ht="13.55" customHeight="1">
       <c r="A49" t="s" s="5">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B49" t="s" s="5">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C49" t="s" s="5">
         <v>12</v>
@@ -4158,10 +4269,10 @@
     </row>
     <row r="50" ht="13.55" customHeight="1">
       <c r="A50" t="s" s="5">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B50" t="s" s="5">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C50" t="s" s="5">
         <v>12</v>
@@ -4188,13 +4299,13 @@
     </row>
     <row r="51" ht="13.55" customHeight="1">
       <c r="A51" t="s" s="5">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B51" t="s" s="5">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C51" t="s" s="5">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D51" t="s" s="5">
         <v>37</v>
@@ -4218,16 +4329,16 @@
     </row>
     <row r="52" ht="13.55" customHeight="1">
       <c r="A52" t="s" s="5">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B52" t="s" s="5">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C52" t="s" s="5">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D52" t="s" s="5">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E52" t="s" s="5">
         <v>27</v>
@@ -4248,10 +4359,10 @@
     </row>
     <row r="53" ht="13.55" customHeight="1">
       <c r="A53" t="s" s="5">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B53" t="s" s="5">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C53" t="s" s="5">
         <v>20</v>
@@ -4278,16 +4389,16 @@
     </row>
     <row r="54" ht="13.55" customHeight="1">
       <c r="A54" t="s" s="5">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B54" t="s" s="5">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C54" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D54" t="s" s="5">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E54" t="s" s="5">
         <v>14</v>
@@ -4308,16 +4419,16 @@
     </row>
     <row r="55" ht="13.55" customHeight="1">
       <c r="A55" t="s" s="5">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B55" t="s" s="5">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C55" t="s" s="5">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D55" t="s" s="5">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E55" t="s" s="5">
         <v>14</v>
@@ -4338,16 +4449,16 @@
     </row>
     <row r="56" ht="13.55" customHeight="1">
       <c r="A56" t="s" s="5">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B56" t="s" s="5">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C56" t="s" s="5">
         <v>30</v>
       </c>
       <c r="D56" t="s" s="5">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E56" t="s" s="5">
         <v>14</v>
@@ -4368,16 +4479,16 @@
     </row>
     <row r="57" ht="13.55" customHeight="1">
       <c r="A57" t="s" s="5">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B57" t="s" s="5">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C57" t="s" s="5">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D57" t="s" s="5">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E57" t="s" s="5">
         <v>14</v>
@@ -4386,7 +4497,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s" s="5">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H57" t="s" s="5">
         <v>17</v>
@@ -4398,16 +4509,16 @@
     </row>
     <row r="58" ht="13.55" customHeight="1">
       <c r="A58" t="s" s="5">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B58" t="s" s="5">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C58" t="s" s="5">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D58" t="s" s="5">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E58" t="s" s="5">
         <v>14</v>
@@ -4428,10 +4539,10 @@
     </row>
     <row r="59" ht="13.55" customHeight="1">
       <c r="A59" t="s" s="5">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B59" t="s" s="5">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C59" t="s" s="5">
         <v>20</v>
@@ -4458,13 +4569,13 @@
     </row>
     <row r="60" ht="13.55" customHeight="1">
       <c r="A60" t="s" s="5">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B60" t="s" s="5">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C60" t="s" s="5">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D60" t="s" s="5">
         <v>31</v>
@@ -4488,10 +4599,10 @@
     </row>
     <row r="61" ht="13.55" customHeight="1">
       <c r="A61" t="s" s="5">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B61" t="s" s="5">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C61" t="s" s="5">
         <v>12</v>
@@ -4518,13 +4629,13 @@
     </row>
     <row r="62" ht="13.55" customHeight="1">
       <c r="A62" t="s" s="5">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B62" t="s" s="5">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C62" t="s" s="5">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D62" t="s" s="5">
         <v>31</v>
@@ -4548,16 +4659,16 @@
     </row>
     <row r="63" ht="13.55" customHeight="1">
       <c r="A63" t="s" s="5">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B63" t="s" s="5">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C63" t="s" s="5">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D63" t="s" s="5">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E63" t="s" s="5">
         <v>14</v>
@@ -4578,10 +4689,10 @@
     </row>
     <row r="64" ht="13.55" customHeight="1">
       <c r="A64" t="s" s="5">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B64" t="s" s="5">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C64" t="s" s="5">
         <v>25</v>
@@ -4608,10 +4719,10 @@
     </row>
     <row r="65" ht="13.55" customHeight="1">
       <c r="A65" t="s" s="5">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B65" t="s" s="5">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C65" t="s" s="5">
         <v>20</v>
@@ -4638,16 +4749,16 @@
     </row>
     <row r="66" ht="13.55" customHeight="1">
       <c r="A66" t="s" s="5">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B66" t="s" s="5">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C66" t="s" s="5">
         <v>30</v>
       </c>
       <c r="D66" t="s" s="5">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E66" t="s" s="5">
         <v>27</v>
@@ -4668,10 +4779,10 @@
     </row>
     <row r="67" ht="13.55" customHeight="1">
       <c r="A67" t="s" s="5">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B67" t="s" s="5">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C67" t="s" s="5">
         <v>25</v>
@@ -4698,16 +4809,16 @@
     </row>
     <row r="68" ht="13.55" customHeight="1">
       <c r="A68" t="s" s="5">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B68" t="s" s="5">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C68" t="s" s="5">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D68" t="s" s="5">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E68" t="s" s="5">
         <v>14</v>
@@ -4728,16 +4839,16 @@
     </row>
     <row r="69" ht="13.55" customHeight="1">
       <c r="A69" t="s" s="5">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B69" t="s" s="5">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C69" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D69" t="s" s="5">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E69" t="s" s="5">
         <v>14</v>
@@ -4758,16 +4869,16 @@
     </row>
     <row r="70" ht="13.55" customHeight="1">
       <c r="A70" t="s" s="5">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B70" t="s" s="5">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C70" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D70" t="s" s="5">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E70" t="s" s="5">
         <v>14</v>
@@ -4788,16 +4899,16 @@
     </row>
     <row r="71" ht="13.55" customHeight="1">
       <c r="A71" t="s" s="5">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B71" t="s" s="5">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C71" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D71" t="s" s="5">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E71" t="s" s="5">
         <v>14</v>
@@ -4818,10 +4929,10 @@
     </row>
     <row r="72" ht="13.55" customHeight="1">
       <c r="A72" t="s" s="5">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B72" t="s" s="5">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C72" t="s" s="5">
         <v>12</v>
@@ -4848,16 +4959,16 @@
     </row>
     <row r="73" ht="13.55" customHeight="1">
       <c r="A73" t="s" s="5">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B73" t="s" s="5">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C73" t="s" s="5">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D73" t="s" s="5">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E73" t="s" s="5">
         <v>14</v>
@@ -4878,16 +4989,16 @@
     </row>
     <row r="74" ht="13.55" customHeight="1">
       <c r="A74" t="s" s="5">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B74" t="s" s="5">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C74" t="s" s="5">
         <v>20</v>
       </c>
       <c r="D74" t="s" s="5">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E74" t="s" s="5">
         <v>14</v>
@@ -4908,10 +5019,10 @@
     </row>
     <row r="75" ht="13.55" customHeight="1">
       <c r="A75" t="s" s="5">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B75" t="s" s="5">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C75" t="s" s="5">
         <v>12</v>
@@ -4938,16 +5049,16 @@
     </row>
     <row r="76" ht="13.55" customHeight="1">
       <c r="A76" t="s" s="5">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B76" t="s" s="5">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C76" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D76" t="s" s="5">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E76" t="s" s="5">
         <v>14</v>
@@ -4970,16 +5081,16 @@
     </row>
     <row r="77" ht="13.55" customHeight="1">
       <c r="A77" t="s" s="5">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B77" t="s" s="5">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C77" t="s" s="5">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D77" t="s" s="5">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E77" t="s" s="5">
         <v>14</v>
@@ -4988,7 +5099,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s" s="5">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H77" t="s" s="5">
         <v>16</v>
@@ -5002,16 +5113,16 @@
     </row>
     <row r="78" ht="13.55" customHeight="1">
       <c r="A78" t="s" s="5">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B78" t="s" s="5">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C78" t="s" s="5">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D78" t="s" s="5">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E78" t="s" s="5">
         <v>14</v>
@@ -5032,13 +5143,13 @@
     </row>
     <row r="79" ht="13.55" customHeight="1">
       <c r="A79" t="s" s="5">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B79" t="s" s="5">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C79" t="s" s="5">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D79" t="s" s="5">
         <v>56</v>
@@ -5062,16 +5173,16 @@
     </row>
     <row r="80" ht="13.55" customHeight="1">
       <c r="A80" t="s" s="5">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B80" t="s" s="5">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C80" t="s" s="5">
         <v>12</v>
       </c>
       <c r="D80" t="s" s="5">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E80" t="s" s="5">
         <v>14</v>
@@ -5092,16 +5203,16 @@
     </row>
     <row r="81" ht="13.55" customHeight="1">
       <c r="A81" t="s" s="5">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B81" t="s" s="5">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C81" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D81" t="s" s="5">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E81" t="s" s="5">
         <v>14</v>
@@ -5122,10 +5233,10 @@
     </row>
     <row r="82" ht="13.55" customHeight="1">
       <c r="A82" t="s" s="5">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B82" t="s" s="5">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C82" t="s" s="5">
         <v>12</v>
@@ -5152,16 +5263,16 @@
     </row>
     <row r="83" ht="13.55" customHeight="1">
       <c r="A83" t="s" s="5">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B83" t="s" s="5">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C83" t="s" s="5">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D83" t="s" s="5">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E83" t="s" s="5">
         <v>14</v>
@@ -5182,10 +5293,10 @@
     </row>
     <row r="84" ht="13.55" customHeight="1">
       <c r="A84" t="s" s="5">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B84" t="s" s="5">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C84" t="s" s="5">
         <v>12</v>
@@ -5212,16 +5323,16 @@
     </row>
     <row r="85" ht="13.55" customHeight="1">
       <c r="A85" t="s" s="5">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B85" t="s" s="5">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C85" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D85" t="s" s="5">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E85" t="s" s="5">
         <v>14</v>
@@ -5242,16 +5353,16 @@
     </row>
     <row r="86" ht="13.55" customHeight="1">
       <c r="A86" t="s" s="5">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B86" t="s" s="5">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C86" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D86" t="s" s="5">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E86" t="s" s="5">
         <v>14</v>
@@ -5274,16 +5385,16 @@
     </row>
     <row r="87" ht="13.55" customHeight="1">
       <c r="A87" t="s" s="5">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B87" t="s" s="5">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C87" t="s" s="5">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D87" t="s" s="5">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E87" t="s" s="5">
         <v>14</v>
@@ -5304,13 +5415,13 @@
     </row>
     <row r="88" ht="13.55" customHeight="1">
       <c r="A88" t="s" s="5">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B88" t="s" s="5">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C88" t="s" s="5">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D88" t="s" s="5">
         <v>71</v>
@@ -5334,13 +5445,13 @@
     </row>
     <row r="89" ht="13.55" customHeight="1">
       <c r="A89" t="s" s="5">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B89" t="s" s="5">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C89" t="s" s="5">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D89" t="s" s="5">
         <v>71</v>
@@ -5366,13 +5477,13 @@
     </row>
     <row r="90" ht="13.55" customHeight="1">
       <c r="A90" t="s" s="5">
+        <v>242</v>
+      </c>
+      <c r="B90" t="s" s="5">
         <v>240</v>
       </c>
-      <c r="B90" t="s" s="5">
-        <v>238</v>
-      </c>
       <c r="C90" t="s" s="5">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D90" t="s" s="5">
         <v>71</v>
@@ -5398,16 +5509,16 @@
     </row>
     <row r="91" ht="13.55" customHeight="1">
       <c r="A91" t="s" s="5">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B91" t="s" s="5">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C91" t="s" s="5">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D91" t="s" s="5">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E91" t="s" s="5">
         <v>14</v>
@@ -5428,13 +5539,13 @@
     </row>
     <row r="92" ht="13.55" customHeight="1">
       <c r="A92" t="s" s="5">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B92" t="s" s="5">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C92" t="s" s="5">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D92" t="s" s="5">
         <v>56</v>
@@ -5458,10 +5569,10 @@
     </row>
     <row r="93" ht="13.55" customHeight="1">
       <c r="A93" t="s" s="5">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B93" t="s" s="5">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C93" t="s" s="5">
         <v>12</v>
@@ -5488,16 +5599,16 @@
     </row>
     <row r="94" ht="13.55" customHeight="1">
       <c r="A94" t="s" s="5">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B94" t="s" s="5">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C94" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D94" t="s" s="5">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E94" t="s" s="5">
         <v>14</v>
@@ -5518,10 +5629,10 @@
     </row>
     <row r="95" ht="13.55" customHeight="1">
       <c r="A95" t="s" s="5">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B95" t="s" s="5">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C95" t="s" s="5">
         <v>25</v>
@@ -5548,10 +5659,10 @@
     </row>
     <row r="96" ht="13.55" customHeight="1">
       <c r="A96" t="s" s="5">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B96" t="s" s="5">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C96" t="s" s="5">
         <v>25</v>
@@ -5578,16 +5689,16 @@
     </row>
     <row r="97" ht="13.55" customHeight="1">
       <c r="A97" t="s" s="5">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B97" t="s" s="5">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C97" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D97" t="s" s="5">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E97" t="s" s="5">
         <v>14</v>
@@ -5608,10 +5719,10 @@
     </row>
     <row r="98" ht="13.55" customHeight="1">
       <c r="A98" t="s" s="5">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B98" t="s" s="5">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C98" t="s" s="5">
         <v>25</v>
@@ -5638,16 +5749,16 @@
     </row>
     <row r="99" ht="13.55" customHeight="1">
       <c r="A99" t="s" s="5">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B99" t="s" s="5">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C99" t="s" s="5">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D99" t="s" s="5">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E99" t="s" s="5">
         <v>14</v>
@@ -5668,16 +5779,16 @@
     </row>
     <row r="100" ht="13.55" customHeight="1">
       <c r="A100" t="s" s="5">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B100" t="s" s="5">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C100" t="s" s="5">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D100" t="s" s="5">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E100" t="s" s="5">
         <v>14</v>
@@ -5698,10 +5809,10 @@
     </row>
     <row r="101" ht="13.55" customHeight="1">
       <c r="A101" t="s" s="5">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B101" t="s" s="5">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C101" t="s" s="5">
         <v>25</v>
@@ -5728,13 +5839,13 @@
     </row>
     <row r="102" ht="13.55" customHeight="1">
       <c r="A102" t="s" s="5">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B102" t="s" s="5">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C102" t="s" s="5">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D102" t="s" s="5">
         <v>31</v>
@@ -5746,7 +5857,7 @@
         <v>15</v>
       </c>
       <c r="G102" t="s" s="5">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H102" t="s" s="5">
         <v>16</v>
@@ -5758,16 +5869,16 @@
     </row>
     <row r="103" ht="13.55" customHeight="1">
       <c r="A103" t="s" s="5">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B103" t="s" s="5">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C103" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D103" t="s" s="5">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E103" t="s" s="5">
         <v>14</v>
@@ -5788,13 +5899,13 @@
     </row>
     <row r="104" ht="13.55" customHeight="1">
       <c r="A104" t="s" s="5">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B104" t="s" s="5">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C104" t="s" s="5">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D104" t="s" s="5">
         <v>13</v>
@@ -5818,10 +5929,10 @@
     </row>
     <row r="105" ht="13.55" customHeight="1">
       <c r="A105" t="s" s="5">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B105" t="s" s="5">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C105" t="s" s="5">
         <v>25</v>
@@ -5848,10 +5959,10 @@
     </row>
     <row r="106" ht="13.55" customHeight="1">
       <c r="A106" t="s" s="5">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B106" t="s" s="5">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C106" t="s" s="5">
         <v>25</v>
@@ -5878,16 +5989,16 @@
     </row>
     <row r="107" ht="13.55" customHeight="1">
       <c r="A107" t="s" s="5">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B107" t="s" s="5">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C107" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D107" t="s" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E107" t="s" s="5">
         <v>27</v>
@@ -5910,10 +6021,10 @@
     </row>
     <row r="108" ht="13.55" customHeight="1">
       <c r="A108" t="s" s="5">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B108" t="s" s="5">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C108" t="s" s="5">
         <v>12</v>
@@ -5940,16 +6051,16 @@
     </row>
     <row r="109" ht="13.55" customHeight="1">
       <c r="A109" t="s" s="5">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B109" t="s" s="5">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C109" t="s" s="5">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D109" t="s" s="5">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E109" t="s" s="5">
         <v>27</v>
@@ -5958,7 +6069,7 @@
         <v>15</v>
       </c>
       <c r="G109" t="s" s="5">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H109" t="s" s="5">
         <v>16</v>
@@ -5970,16 +6081,16 @@
     </row>
     <row r="110" ht="13.55" customHeight="1">
       <c r="A110" t="s" s="5">
+        <v>288</v>
+      </c>
+      <c r="B110" t="s" s="5">
+        <v>285</v>
+      </c>
+      <c r="C110" t="s" s="5">
         <v>286</v>
       </c>
-      <c r="B110" t="s" s="5">
-        <v>283</v>
-      </c>
-      <c r="C110" t="s" s="5">
-        <v>284</v>
-      </c>
       <c r="D110" t="s" s="5">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E110" t="s" s="5">
         <v>14</v>
@@ -5988,7 +6099,7 @@
         <v>15</v>
       </c>
       <c r="G110" t="s" s="5">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H110" t="s" s="5">
         <v>16</v>
@@ -6002,10 +6113,10 @@
     </row>
     <row r="111" ht="13.55" customHeight="1">
       <c r="A111" t="s" s="5">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B111" t="s" s="5">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C111" t="s" s="5">
         <v>25</v>
@@ -6032,16 +6143,16 @@
     </row>
     <row r="112" ht="13.55" customHeight="1">
       <c r="A112" t="s" s="5">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B112" t="s" s="5">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C112" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D112" t="s" s="5">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E112" t="s" s="5">
         <v>14</v>
@@ -6062,16 +6173,16 @@
     </row>
     <row r="113" ht="13.55" customHeight="1">
       <c r="A113" t="s" s="5">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B113" t="s" s="5">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C113" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D113" t="s" s="5">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E113" t="s" s="5">
         <v>14</v>
@@ -6092,16 +6203,16 @@
     </row>
     <row r="114" ht="13.55" customHeight="1">
       <c r="A114" t="s" s="5">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B114" t="s" s="5">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C114" t="s" s="5">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D114" t="s" s="5">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E114" t="s" s="5">
         <v>14</v>
@@ -6110,7 +6221,7 @@
         <v>15</v>
       </c>
       <c r="G114" t="s" s="5">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H114" t="s" s="5">
         <v>16</v>
@@ -6122,10 +6233,10 @@
     </row>
     <row r="115" ht="13.55" customHeight="1">
       <c r="A115" t="s" s="5">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B115" t="s" s="5">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C115" t="s" s="5">
         <v>30</v>
@@ -6152,10 +6263,10 @@
     </row>
     <row r="116" ht="13.55" customHeight="1">
       <c r="A116" t="s" s="5">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B116" t="s" s="5">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C116" t="s" s="5">
         <v>12</v>
@@ -6182,16 +6293,16 @@
     </row>
     <row r="117" ht="13.55" customHeight="1">
       <c r="A117" t="s" s="5">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B117" t="s" s="5">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C117" t="s" s="5">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D117" t="s" s="5">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E117" t="s" s="5">
         <v>14</v>
@@ -6200,7 +6311,7 @@
         <v>15</v>
       </c>
       <c r="G117" t="s" s="5">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H117" t="s" s="5">
         <v>16</v>
@@ -6214,16 +6325,16 @@
     </row>
     <row r="118" ht="13.55" customHeight="1">
       <c r="A118" t="s" s="5">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B118" t="s" s="5">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C118" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D118" t="s" s="5">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E118" t="s" s="5">
         <v>14</v>
@@ -6244,16 +6355,16 @@
     </row>
     <row r="119" ht="13.55" customHeight="1">
       <c r="A119" t="s" s="5">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B119" t="s" s="5">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C119" t="s" s="5">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D119" t="s" s="5">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E119" t="s" s="5">
         <v>14</v>
@@ -6274,10 +6385,10 @@
     </row>
     <row r="120" ht="13.55" customHeight="1">
       <c r="A120" t="s" s="5">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B120" t="s" s="5">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C120" t="s" s="5">
         <v>25</v>
@@ -6304,16 +6415,16 @@
     </row>
     <row r="121" ht="13.55" customHeight="1">
       <c r="A121" t="s" s="5">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B121" t="s" s="5">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C121" t="s" s="5">
         <v>12</v>
       </c>
       <c r="D121" t="s" s="5">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E121" t="s" s="5">
         <v>14</v>
@@ -6334,13 +6445,13 @@
     </row>
     <row r="122" ht="13.55" customHeight="1">
       <c r="A122" t="s" s="5">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B122" t="s" s="5">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C122" t="s" s="5">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D122" t="s" s="5">
         <v>56</v>
@@ -6364,13 +6475,13 @@
     </row>
     <row r="123" ht="13.55" customHeight="1">
       <c r="A123" t="s" s="5">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B123" t="s" s="5">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C123" t="s" s="5">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D123" t="s" s="5">
         <v>71</v>
@@ -6394,16 +6505,16 @@
     </row>
     <row r="124" ht="13.55" customHeight="1">
       <c r="A124" t="s" s="5">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B124" t="s" s="5">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C124" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D124" t="s" s="5">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="E124" t="s" s="5">
         <v>14</v>
@@ -6424,13 +6535,13 @@
     </row>
     <row r="125" ht="13.55" customHeight="1">
       <c r="A125" t="s" s="5">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B125" t="s" s="5">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C125" t="s" s="5">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D125" t="s" s="5">
         <v>71</v>
@@ -6456,13 +6567,13 @@
     </row>
     <row r="126" ht="13.55" customHeight="1">
       <c r="A126" t="s" s="5">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B126" t="s" s="5">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C126" t="s" s="5">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D126" t="s" s="5">
         <v>68</v>
@@ -6486,16 +6597,16 @@
     </row>
     <row r="127" ht="13.55" customHeight="1">
       <c r="A127" t="s" s="5">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B127" t="s" s="5">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C127" t="s" s="5">
         <v>20</v>
       </c>
       <c r="D127" t="s" s="5">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E127" t="s" s="5">
         <v>14</v>
@@ -6516,16 +6627,16 @@
     </row>
     <row r="128" ht="13.55" customHeight="1">
       <c r="A128" t="s" s="5">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B128" t="s" s="5">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C128" t="s" s="5">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D128" t="s" s="5">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E128" t="s" s="5">
         <v>14</v>
@@ -6534,7 +6645,7 @@
         <v>15</v>
       </c>
       <c r="G128" t="s" s="5">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H128" t="s" s="5">
         <v>16</v>
@@ -6546,16 +6657,16 @@
     </row>
     <row r="129" ht="13.55" customHeight="1">
       <c r="A129" t="s" s="5">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B129" t="s" s="5">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C129" t="s" s="5">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D129" t="s" s="5">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E129" t="s" s="5">
         <v>14</v>
@@ -6564,7 +6675,7 @@
         <v>15</v>
       </c>
       <c r="G129" t="s" s="5">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H129" t="s" s="5">
         <v>16</v>
@@ -6576,16 +6687,16 @@
     </row>
     <row r="130" ht="13.55" customHeight="1">
       <c r="A130" t="s" s="5">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B130" t="s" s="5">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C130" t="s" s="5">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D130" t="s" s="5">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E130" t="s" s="5">
         <v>14</v>
@@ -6606,13 +6717,13 @@
     </row>
     <row r="131" ht="13.55" customHeight="1">
       <c r="A131" t="s" s="5">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B131" t="s" s="5">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C131" t="s" s="5">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D131" t="s" s="5">
         <v>71</v>
@@ -6636,13 +6747,13 @@
     </row>
     <row r="132" ht="13.55" customHeight="1">
       <c r="A132" t="s" s="5">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B132" t="s" s="5">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C132" t="s" s="5">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D132" t="s" s="5">
         <v>71</v>
@@ -6666,13 +6777,13 @@
     </row>
     <row r="133" ht="13.55" customHeight="1">
       <c r="A133" t="s" s="5">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B133" t="s" s="5">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C133" t="s" s="5">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D133" t="s" s="5">
         <v>56</v>
@@ -6696,10 +6807,10 @@
     </row>
     <row r="134" ht="13.55" customHeight="1">
       <c r="A134" t="s" s="5">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B134" t="s" s="5">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C134" t="s" s="5">
         <v>12</v>
@@ -6726,10 +6837,10 @@
     </row>
     <row r="135" ht="13.55" customHeight="1">
       <c r="A135" t="s" s="5">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B135" t="s" s="5">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C135" t="s" s="5">
         <v>12</v>
@@ -6756,10 +6867,10 @@
     </row>
     <row r="136" ht="13.55" customHeight="1">
       <c r="A136" t="s" s="5">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B136" t="s" s="5">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C136" t="s" s="5">
         <v>25</v>
@@ -6786,13 +6897,13 @@
     </row>
     <row r="137" ht="13.55" customHeight="1">
       <c r="A137" t="s" s="5">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B137" t="s" s="5">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C137" t="s" s="5">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D137" t="s" s="5">
         <v>56</v>
@@ -6818,10 +6929,10 @@
     </row>
     <row r="138" ht="13.55" customHeight="1">
       <c r="A138" t="s" s="5">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B138" t="s" s="5">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C138" t="s" s="5">
         <v>25</v>
@@ -6848,10 +6959,10 @@
     </row>
     <row r="139" ht="13.55" customHeight="1">
       <c r="A139" t="s" s="5">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B139" t="s" s="5">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C139" t="s" s="5">
         <v>25</v>
@@ -6878,10 +6989,10 @@
     </row>
     <row r="140" ht="13.55" customHeight="1">
       <c r="A140" t="s" s="5">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B140" t="s" s="5">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C140" t="s" s="5">
         <v>25</v>
@@ -6910,16 +7021,16 @@
     </row>
     <row r="141" ht="13.55" customHeight="1">
       <c r="A141" t="s" s="5">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B141" t="s" s="5">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C141" t="s" s="5">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D141" t="s" s="5">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E141" t="s" s="5">
         <v>14</v>
@@ -6928,7 +7039,7 @@
         <v>15</v>
       </c>
       <c r="G141" t="s" s="5">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H141" t="s" s="5">
         <v>16</v>
@@ -6940,13 +7051,13 @@
     </row>
     <row r="142" ht="13.55" customHeight="1">
       <c r="A142" t="s" s="5">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B142" t="s" s="5">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C142" t="s" s="5">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D142" t="s" s="5">
         <v>71</v>
@@ -6970,10 +7081,10 @@
     </row>
     <row r="143" ht="13.55" customHeight="1">
       <c r="A143" t="s" s="5">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B143" t="s" s="5">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C143" t="s" s="5">
         <v>25</v>
@@ -7000,10 +7111,10 @@
     </row>
     <row r="144" ht="13.55" customHeight="1">
       <c r="A144" t="s" s="5">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B144" t="s" s="5">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C144" t="s" s="5">
         <v>12</v>
@@ -7030,10 +7141,10 @@
     </row>
     <row r="145" ht="13.55" customHeight="1">
       <c r="A145" t="s" s="5">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B145" t="s" s="5">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C145" t="s" s="5">
         <v>12</v>
@@ -7060,16 +7171,16 @@
     </row>
     <row r="146" ht="13.55" customHeight="1">
       <c r="A146" t="s" s="5">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B146" t="s" s="5">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C146" t="s" s="5">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D146" t="s" s="5">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E146" t="s" s="5">
         <v>14</v>
@@ -7090,13 +7201,13 @@
     </row>
     <row r="147" ht="13.55" customHeight="1">
       <c r="A147" t="s" s="5">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B147" t="s" s="5">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C147" t="s" s="5">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D147" t="s" s="5">
         <v>71</v>
@@ -7120,16 +7231,16 @@
     </row>
     <row r="148" ht="13.55" customHeight="1">
       <c r="A148" t="s" s="5">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B148" t="s" s="5">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C148" t="s" s="5">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D148" t="s" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E148" t="s" s="5">
         <v>14</v>
@@ -7152,16 +7263,16 @@
     </row>
     <row r="149" ht="13.55" customHeight="1">
       <c r="A149" t="s" s="5">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B149" t="s" s="5">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C149" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D149" t="s" s="5">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E149" t="s" s="5">
         <v>14</v>
@@ -7184,16 +7295,16 @@
     </row>
     <row r="150" ht="13.55" customHeight="1">
       <c r="A150" t="s" s="5">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B150" t="s" s="5">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C150" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D150" t="s" s="5">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E150" t="s" s="5">
         <v>14</v>
@@ -7216,16 +7327,16 @@
     </row>
     <row r="151" ht="13.55" customHeight="1">
       <c r="A151" t="s" s="5">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B151" t="s" s="5">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C151" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D151" t="s" s="5">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E151" t="s" s="5">
         <v>14</v>
@@ -7246,10 +7357,10 @@
     </row>
     <row r="152" ht="13.55" customHeight="1">
       <c r="A152" t="s" s="5">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B152" t="s" s="5">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C152" t="s" s="5">
         <v>25</v>
@@ -7276,16 +7387,16 @@
     </row>
     <row r="153" ht="13.55" customHeight="1">
       <c r="A153" t="s" s="5">
+        <v>373</v>
+      </c>
+      <c r="B153" t="s" s="5">
         <v>370</v>
-      </c>
-      <c r="B153" t="s" s="5">
-        <v>367</v>
       </c>
       <c r="C153" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D153" t="s" s="5">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E153" t="s" s="5">
         <v>14</v>
@@ -7306,16 +7417,16 @@
     </row>
     <row r="154" ht="13.55" customHeight="1">
       <c r="A154" t="s" s="5">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B154" t="s" s="5">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C154" t="s" s="5">
         <v>63</v>
       </c>
       <c r="D154" t="s" s="5">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E154" t="s" s="5">
         <v>14</v>
@@ -7324,7 +7435,7 @@
         <v>48</v>
       </c>
       <c r="G154" t="s" s="5">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="H154" t="s" s="5">
         <v>16</v>
@@ -7338,10 +7449,10 @@
     </row>
     <row r="155" ht="13.55" customHeight="1">
       <c r="A155" t="s" s="5">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B155" t="s" s="5">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C155" t="s" s="5">
         <v>25</v>
@@ -7370,10 +7481,10 @@
     </row>
     <row r="156" ht="13.55" customHeight="1">
       <c r="A156" t="s" s="5">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B156" t="s" s="5">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C156" t="s" s="5">
         <v>12</v>
@@ -7400,16 +7511,16 @@
     </row>
     <row r="157" ht="13.55" customHeight="1">
       <c r="A157" t="s" s="5">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B157" t="s" s="5">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C157" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D157" t="s" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E157" t="s" s="5">
         <v>14</v>
@@ -7432,16 +7543,16 @@
     </row>
     <row r="158" ht="13.55" customHeight="1">
       <c r="A158" t="s" s="5">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B158" t="s" s="5">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C158" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D158" t="s" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E158" t="s" s="5">
         <v>14</v>
@@ -7462,10 +7573,10 @@
     </row>
     <row r="159" ht="13.55" customHeight="1">
       <c r="A159" t="s" s="5">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B159" t="s" s="5">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C159" t="s" s="5">
         <v>12</v>
@@ -7494,10 +7605,10 @@
     </row>
     <row r="160" ht="13.55" customHeight="1">
       <c r="A160" t="s" s="5">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B160" t="s" s="5">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C160" t="s" s="5">
         <v>25</v>
@@ -7524,16 +7635,16 @@
     </row>
     <row r="161" ht="13.55" customHeight="1">
       <c r="A161" t="s" s="5">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B161" t="s" s="5">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C161" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D161" t="s" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E161" t="s" s="5">
         <v>27</v>
@@ -7556,16 +7667,16 @@
     </row>
     <row r="162" ht="13.55" customHeight="1">
       <c r="A162" t="s" s="5">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B162" t="s" s="5">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C162" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D162" t="s" s="5">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E162" t="s" s="5">
         <v>14</v>
@@ -7588,10 +7699,10 @@
     </row>
     <row r="163" ht="13.55" customHeight="1">
       <c r="A163" t="s" s="5">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B163" t="s" s="5">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C163" t="s" s="5">
         <v>25</v>
@@ -7618,16 +7729,16 @@
     </row>
     <row r="164" ht="13.55" customHeight="1">
       <c r="A164" t="s" s="5">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B164" t="s" s="5">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C164" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D164" t="s" s="5">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E164" t="s" s="5">
         <v>27</v>
@@ -7648,13 +7759,13 @@
     </row>
     <row r="165" ht="13.55" customHeight="1">
       <c r="A165" t="s" s="5">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B165" t="s" s="5">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C165" t="s" s="5">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D165" t="s" s="5">
         <v>71</v>
@@ -7666,7 +7777,7 @@
         <v>48</v>
       </c>
       <c r="G165" t="s" s="5">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H165" t="s" s="5">
         <v>16</v>
@@ -7678,16 +7789,16 @@
     </row>
     <row r="166" ht="13.55" customHeight="1">
       <c r="A166" t="s" s="5">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B166" t="s" s="5">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C166" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D166" t="s" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E166" t="s" s="5">
         <v>27</v>
@@ -7708,16 +7819,16 @@
     </row>
     <row r="167" ht="13.55" customHeight="1">
       <c r="A167" t="s" s="5">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B167" t="s" s="5">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C167" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D167" t="s" s="5">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E167" t="s" s="5">
         <v>14</v>
@@ -7738,10 +7849,10 @@
     </row>
     <row r="168" ht="13.55" customHeight="1">
       <c r="A168" t="s" s="5">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B168" t="s" s="5">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C168" t="s" s="5">
         <v>25</v>
@@ -7768,16 +7879,16 @@
     </row>
     <row r="169" ht="13.55" customHeight="1">
       <c r="A169" t="s" s="5">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B169" t="s" s="5">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C169" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D169" t="s" s="5">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E169" t="s" s="5">
         <v>14</v>
@@ -7798,10 +7909,10 @@
     </row>
     <row r="170" ht="13.55" customHeight="1">
       <c r="A170" t="s" s="5">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B170" t="s" s="5">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C170" t="s" s="5">
         <v>12</v>
@@ -7828,13 +7939,13 @@
     </row>
     <row r="171" ht="13.55" customHeight="1">
       <c r="A171" t="s" s="5">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B171" t="s" s="5">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C171" t="s" s="5">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D171" t="s" s="5">
         <v>71</v>
@@ -7858,13 +7969,13 @@
     </row>
     <row r="172" ht="13.55" customHeight="1">
       <c r="A172" t="s" s="5">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B172" t="s" s="5">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C172" t="s" s="5">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D172" t="s" s="5">
         <v>71</v>
@@ -7876,7 +7987,7 @@
         <v>48</v>
       </c>
       <c r="G172" t="s" s="5">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H172" t="s" s="5">
         <v>16</v>
@@ -7888,16 +7999,16 @@
     </row>
     <row r="173" ht="13.55" customHeight="1">
       <c r="A173" t="s" s="5">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B173" t="s" s="5">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C173" t="s" s="5">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D173" t="s" s="5">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E173" t="s" s="5">
         <v>27</v>
@@ -7906,10 +8017,10 @@
         <v>15</v>
       </c>
       <c r="G173" t="s" s="5">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="H173" t="s" s="5">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="I173" s="7"/>
       <c r="J173" s="6">
@@ -7918,16 +8029,16 @@
     </row>
     <row r="174" ht="13.55" customHeight="1">
       <c r="A174" t="s" s="5">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B174" t="s" s="5">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C174" t="s" s="5">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D174" t="s" s="5">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E174" t="s" s="5">
         <v>14</v>
@@ -7936,10 +8047,10 @@
         <v>48</v>
       </c>
       <c r="G174" t="s" s="5">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="H174" t="s" s="5">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="I174" s="7"/>
       <c r="J174" s="6">
@@ -7948,28 +8059,28 @@
     </row>
     <row r="175" ht="13.55" customHeight="1">
       <c r="A175" t="s" s="5">
+        <v>418</v>
+      </c>
+      <c r="B175" t="s" s="5">
+        <v>419</v>
+      </c>
+      <c r="C175" t="s" s="5">
+        <v>229</v>
+      </c>
+      <c r="D175" t="s" s="5">
+        <v>148</v>
+      </c>
+      <c r="E175" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F175" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G175" t="s" s="5">
         <v>415</v>
       </c>
-      <c r="B175" t="s" s="5">
-        <v>416</v>
-      </c>
-      <c r="C175" t="s" s="5">
-        <v>227</v>
-      </c>
-      <c r="D175" t="s" s="5">
-        <v>146</v>
-      </c>
-      <c r="E175" t="s" s="5">
-        <v>14</v>
-      </c>
-      <c r="F175" t="s" s="5">
-        <v>48</v>
-      </c>
-      <c r="G175" t="s" s="5">
-        <v>412</v>
-      </c>
       <c r="H175" t="s" s="5">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="I175" s="7"/>
       <c r="J175" s="6">
@@ -7978,10 +8089,10 @@
     </row>
     <row r="176" ht="13.55" customHeight="1">
       <c r="A176" t="s" s="5">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B176" t="s" s="5">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C176" t="s" s="5">
         <v>25</v>
@@ -8010,16 +8121,16 @@
     </row>
     <row r="177" ht="13.55" customHeight="1">
       <c r="A177" t="s" s="5">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B177" t="s" s="5">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C177" t="s" s="5">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D177" t="s" s="5">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="E177" t="s" s="5">
         <v>14</v>
@@ -8028,10 +8139,10 @@
         <v>48</v>
       </c>
       <c r="G177" t="s" s="5">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="H177" t="s" s="5">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="I177" s="7"/>
       <c r="J177" s="6">
@@ -8040,16 +8151,16 @@
     </row>
     <row r="178" ht="13.55" customHeight="1">
       <c r="A178" t="s" s="5">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B178" t="s" s="5">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C178" t="s" s="5">
         <v>12</v>
       </c>
       <c r="D178" t="s" s="5">
-        <v>364</v>
+        <v>426</v>
       </c>
       <c r="E178" t="s" s="5">
         <v>14</v>
@@ -8070,16 +8181,16 @@
     </row>
     <row r="179" ht="13.55" customHeight="1">
       <c r="A179" t="s" s="5">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B179" t="s" s="5">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C179" t="s" s="5">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D179" t="s" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E179" t="s" s="5">
         <v>14</v>
@@ -8088,7 +8199,7 @@
         <v>48</v>
       </c>
       <c r="G179" t="s" s="5">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H179" t="s" s="5">
         <v>16</v>
@@ -8100,16 +8211,16 @@
     </row>
     <row r="180" ht="13.55" customHeight="1">
       <c r="A180" t="s" s="5">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B180" t="s" s="5">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C180" t="s" s="5">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D180" t="s" s="5">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E180" t="s" s="5">
         <v>14</v>
@@ -8118,10 +8229,10 @@
         <v>48</v>
       </c>
       <c r="G180" t="s" s="5">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="H180" t="s" s="5">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="I180" s="7"/>
       <c r="J180" s="6">
@@ -8130,10 +8241,10 @@
     </row>
     <row r="181" ht="13.55" customHeight="1">
       <c r="A181" t="s" s="5">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B181" t="s" s="5">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C181" t="s" s="5">
         <v>25</v>
@@ -8160,16 +8271,16 @@
     </row>
     <row r="182" ht="13.55" customHeight="1">
       <c r="A182" t="s" s="5">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B182" t="s" s="5">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C182" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D182" t="s" s="5">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E182" t="s" s="5">
         <v>14</v>
@@ -8192,16 +8303,16 @@
     </row>
     <row r="183" ht="13.55" customHeight="1">
       <c r="A183" t="s" s="5">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B183" t="s" s="5">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C183" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D183" t="s" s="5">
-        <v>364</v>
+        <v>426</v>
       </c>
       <c r="E183" t="s" s="5">
         <v>14</v>
@@ -8224,10 +8335,10 @@
     </row>
     <row r="184" ht="13.55" customHeight="1">
       <c r="A184" t="s" s="5">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B184" t="s" s="5">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C184" t="s" s="5">
         <v>25</v>
@@ -8256,16 +8367,16 @@
     </row>
     <row r="185" ht="13.55" customHeight="1">
       <c r="A185" t="s" s="5">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B185" t="s" s="5">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C185" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D185" t="s" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E185" t="s" s="5">
         <v>14</v>
@@ -8288,16 +8399,16 @@
     </row>
     <row r="186" ht="13.55" customHeight="1">
       <c r="A186" t="s" s="5">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B186" t="s" s="5">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C186" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D186" t="s" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E186" t="s" s="5">
         <v>14</v>
@@ -8320,13 +8431,13 @@
     </row>
     <row r="187" ht="13.55" customHeight="1">
       <c r="A187" t="s" s="5">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B187" t="s" s="5">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C187" t="s" s="5">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D187" t="s" s="5">
         <v>71</v>
@@ -8350,13 +8461,13 @@
     </row>
     <row r="188" ht="13.55" customHeight="1">
       <c r="A188" t="s" s="5">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B188" t="s" s="5">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C188" t="s" s="5">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D188" t="s" s="5">
         <v>71</v>
@@ -8380,10 +8491,10 @@
     </row>
     <row r="189" ht="13.55" customHeight="1">
       <c r="A189" t="s" s="5">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B189" t="s" s="5">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C189" t="s" s="5">
         <v>25</v>
@@ -8412,10 +8523,10 @@
     </row>
     <row r="190" ht="13.55" customHeight="1">
       <c r="A190" t="s" s="5">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B190" t="s" s="5">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C190" t="s" s="5">
         <v>25</v>
@@ -8444,10 +8555,10 @@
     </row>
     <row r="191" ht="13.55" customHeight="1">
       <c r="A191" t="s" s="5">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B191" t="s" s="5">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C191" t="s" s="5">
         <v>25</v>
@@ -8476,16 +8587,16 @@
     </row>
     <row r="192" ht="13.55" customHeight="1">
       <c r="A192" t="s" s="5">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B192" t="s" s="5">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C192" t="s" s="5">
         <v>12</v>
       </c>
       <c r="D192" t="s" s="5">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E192" t="s" s="5">
         <v>14</v>
@@ -8506,16 +8617,16 @@
     </row>
     <row r="193" ht="13.55" customHeight="1">
       <c r="A193" t="s" s="5">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B193" t="s" s="5">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C193" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D193" t="s" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E193" t="s" s="5">
         <v>14</v>
@@ -8536,16 +8647,16 @@
     </row>
     <row r="194" ht="13.55" customHeight="1">
       <c r="A194" t="s" s="5">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B194" t="s" s="5">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C194" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D194" t="s" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E194" t="s" s="5">
         <v>14</v>
@@ -8566,16 +8677,16 @@
     </row>
     <row r="195" ht="13.55" customHeight="1">
       <c r="A195" t="s" s="5">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B195" t="s" s="5">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C195" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D195" t="s" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E195" t="s" s="5">
         <v>14</v>
@@ -8596,16 +8707,16 @@
     </row>
     <row r="196" ht="13.55" customHeight="1">
       <c r="A196" t="s" s="5">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B196" t="s" s="5">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C196" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D196" t="s" s="5">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E196" t="s" s="5">
         <v>14</v>
@@ -8628,16 +8739,16 @@
     </row>
     <row r="197" ht="13.55" customHeight="1">
       <c r="A197" t="s" s="5">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B197" t="s" s="5">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C197" t="s" s="5">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D197" t="s" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E197" t="s" s="5">
         <v>27</v>
@@ -8646,7 +8757,7 @@
         <v>48</v>
       </c>
       <c r="G197" t="s" s="5">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H197" t="s" s="5">
         <v>16</v>
@@ -8658,16 +8769,16 @@
     </row>
     <row r="198" ht="13.55" customHeight="1">
       <c r="A198" t="s" s="5">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B198" t="s" s="5">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C198" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D198" t="s" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E198" t="s" s="5">
         <v>27</v>
@@ -8690,10 +8801,10 @@
     </row>
     <row r="199" ht="13.55" customHeight="1">
       <c r="A199" t="s" s="5">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B199" t="s" s="5">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C199" t="s" s="5">
         <v>25</v>
@@ -8720,10 +8831,10 @@
     </row>
     <row r="200" ht="13.55" customHeight="1">
       <c r="A200" t="s" s="5">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B200" t="s" s="5">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C200" t="s" s="5">
         <v>12</v>
@@ -8752,16 +8863,16 @@
     </row>
     <row r="201" ht="13.55" customHeight="1">
       <c r="A201" t="s" s="5">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B201" t="s" s="5">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C201" t="s" s="5">
         <v>25</v>
       </c>
       <c r="D201" t="s" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E201" t="s" s="5">
         <v>14</v>
@@ -8784,16 +8895,16 @@
     </row>
     <row r="202" ht="13.55" customHeight="1">
       <c r="A202" t="s" s="5">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B202" t="s" s="5">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C202" t="s" s="5">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D202" t="s" s="5">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E202" t="s" s="5">
         <v>14</v>
@@ -8802,7 +8913,7 @@
         <v>48</v>
       </c>
       <c r="G202" t="s" s="5">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H202" t="s" s="5">
         <v>16</v>
@@ -8814,16 +8925,16 @@
     </row>
     <row r="203" ht="13.55" customHeight="1">
       <c r="A203" t="s" s="5">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B203" t="s" s="5">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C203" t="s" s="5">
         <v>12</v>
       </c>
       <c r="D203" t="s" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E203" t="s" s="5">
         <v>14</v>
@@ -8844,10 +8955,10 @@
     </row>
     <row r="204" ht="13.55" customHeight="1">
       <c r="A204" t="s" s="5">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B204" t="s" s="5">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C204" t="s" s="5">
         <v>25</v>
@@ -8874,16 +8985,16 @@
     </row>
     <row r="205" ht="13.55" customHeight="1">
       <c r="A205" t="s" s="5">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B205" t="s" s="5">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C205" t="s" s="5">
         <v>12</v>
       </c>
       <c r="D205" t="s" s="5">
-        <v>364</v>
+        <v>426</v>
       </c>
       <c r="E205" t="s" s="5">
         <v>14</v>
@@ -8904,16 +9015,16 @@
     </row>
     <row r="206" ht="13.55" customHeight="1">
       <c r="A206" t="s" s="5">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B206" t="s" s="5">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C206" t="s" s="5">
         <v>12</v>
       </c>
       <c r="D206" t="s" s="5">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E206" t="s" s="5">
         <v>14</v>
@@ -8934,16 +9045,16 @@
     </row>
     <row r="207" ht="13.55" customHeight="1">
       <c r="A207" t="s" s="5">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B207" t="s" s="5">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C207" t="s" s="5">
         <v>12</v>
       </c>
       <c r="D207" t="s" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E207" t="s" s="5">
         <v>14</v>
@@ -8964,13 +9075,13 @@
     </row>
     <row r="208" ht="13.55" customHeight="1">
       <c r="A208" t="s" s="5">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B208" t="s" s="5">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C208" t="s" s="5">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D208" t="s" s="5">
         <v>71</v>
@@ -8994,10 +9105,10 @@
     </row>
     <row r="209" ht="13.55" customHeight="1">
       <c r="A209" t="s" s="5">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B209" t="s" s="5">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C209" t="s" s="5">
         <v>12</v>
@@ -9021,6 +9132,350 @@
       <c r="J209" s="6">
         <v>2026</v>
       </c>
+    </row>
+    <row r="210" ht="13.55" customHeight="1">
+      <c r="A210" t="s" s="5">
+        <v>482</v>
+      </c>
+      <c r="B210" t="s" s="5">
+        <v>483</v>
+      </c>
+      <c r="C210" t="s" s="5">
+        <v>100</v>
+      </c>
+      <c r="D210" t="s" s="5">
+        <v>484</v>
+      </c>
+      <c r="E210" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F210" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G210" t="s" s="5">
+        <v>101</v>
+      </c>
+      <c r="H210" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I210" s="7"/>
+      <c r="J210" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="211" ht="13.55" customHeight="1">
+      <c r="A211" t="s" s="5">
+        <v>485</v>
+      </c>
+      <c r="B211" t="s" s="5">
+        <v>486</v>
+      </c>
+      <c r="C211" t="s" s="5">
+        <v>487</v>
+      </c>
+      <c r="D211" t="s" s="5">
+        <v>484</v>
+      </c>
+      <c r="E211" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F211" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G211" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="H211" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I211" s="7"/>
+      <c r="J211" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="212" ht="13.55" customHeight="1">
+      <c r="A212" t="s" s="5">
+        <v>488</v>
+      </c>
+      <c r="B212" t="s" s="5">
+        <v>489</v>
+      </c>
+      <c r="C212" t="s" s="5">
+        <v>12</v>
+      </c>
+      <c r="D212" t="s" s="5">
+        <v>71</v>
+      </c>
+      <c r="E212" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F212" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G212" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="H212" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I212" s="7"/>
+      <c r="J212" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="213" ht="13.55" customHeight="1">
+      <c r="A213" t="s" s="5">
+        <v>490</v>
+      </c>
+      <c r="B213" t="s" s="5">
+        <v>491</v>
+      </c>
+      <c r="C213" t="s" s="5">
+        <v>12</v>
+      </c>
+      <c r="D213" t="s" s="5">
+        <v>492</v>
+      </c>
+      <c r="E213" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F213" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G213" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="H213" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I213" s="7"/>
+      <c r="J213" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="214" ht="13.55" customHeight="1">
+      <c r="A214" t="s" s="5">
+        <v>493</v>
+      </c>
+      <c r="B214" t="s" s="5">
+        <v>494</v>
+      </c>
+      <c r="C214" t="s" s="5">
+        <v>25</v>
+      </c>
+      <c r="D214" t="s" s="5">
+        <v>71</v>
+      </c>
+      <c r="E214" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F214" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G214" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="H214" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I214" s="7"/>
+      <c r="J214" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="215" ht="13.55" customHeight="1">
+      <c r="A215" t="s" s="5">
+        <v>495</v>
+      </c>
+      <c r="B215" t="s" s="5">
+        <v>496</v>
+      </c>
+      <c r="C215" t="s" s="5">
+        <v>12</v>
+      </c>
+      <c r="D215" t="s" s="5">
+        <v>281</v>
+      </c>
+      <c r="E215" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F215" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G215" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="H215" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I215" s="6">
+        <v>10</v>
+      </c>
+      <c r="J215" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="216" ht="13.55" customHeight="1">
+      <c r="A216" t="s" s="5">
+        <v>497</v>
+      </c>
+      <c r="B216" t="s" s="5">
+        <v>498</v>
+      </c>
+      <c r="C216" t="s" s="5">
+        <v>499</v>
+      </c>
+      <c r="D216" t="s" s="5">
+        <v>500</v>
+      </c>
+      <c r="E216" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F216" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G216" t="s" s="5">
+        <v>22</v>
+      </c>
+      <c r="H216" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I216" s="7"/>
+      <c r="J216" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="217" ht="13.55" customHeight="1">
+      <c r="A217" t="s" s="5">
+        <v>501</v>
+      </c>
+      <c r="B217" t="s" s="5">
+        <v>502</v>
+      </c>
+      <c r="C217" t="s" s="5">
+        <v>503</v>
+      </c>
+      <c r="D217" t="s" s="5">
+        <v>504</v>
+      </c>
+      <c r="E217" t="s" s="5">
+        <v>27</v>
+      </c>
+      <c r="F217" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G217" t="s" s="5">
+        <v>164</v>
+      </c>
+      <c r="H217" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I217" s="7"/>
+      <c r="J217" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="218" ht="13.55" customHeight="1">
+      <c r="A218" t="s" s="5">
+        <v>505</v>
+      </c>
+      <c r="B218" t="s" s="5">
+        <v>506</v>
+      </c>
+      <c r="C218" t="s" s="5">
+        <v>173</v>
+      </c>
+      <c r="D218" t="s" s="5">
+        <v>507</v>
+      </c>
+      <c r="E218" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F218" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G218" t="s" s="5">
+        <v>508</v>
+      </c>
+      <c r="H218" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I218" s="7"/>
+      <c r="J218" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="219" ht="13.55" customHeight="1">
+      <c r="A219" t="s" s="5">
+        <v>509</v>
+      </c>
+      <c r="B219" t="s" s="5">
+        <v>510</v>
+      </c>
+      <c r="C219" t="s" s="5">
+        <v>487</v>
+      </c>
+      <c r="D219" t="s" s="5">
+        <v>71</v>
+      </c>
+      <c r="E219" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F219" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G219" t="s" s="5">
+        <v>511</v>
+      </c>
+      <c r="H219" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I219" s="7"/>
+      <c r="J219" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="220" ht="13.55" customHeight="1">
+      <c r="A220" t="s" s="5">
+        <v>512</v>
+      </c>
+      <c r="B220" t="s" s="5">
+        <v>513</v>
+      </c>
+      <c r="C220" t="s" s="5">
+        <v>514</v>
+      </c>
+      <c r="D220" t="s" s="5">
+        <v>71</v>
+      </c>
+      <c r="E220" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F220" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G220" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="H220" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I220" s="7"/>
+      <c r="J220" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="221" ht="13.55" customHeight="1">
+      <c r="A221" s="7"/>
+      <c r="B221" s="7"/>
+      <c r="C221" s="7"/>
+      <c r="D221" s="7"/>
+      <c r="E221" s="7"/>
+      <c r="F221" s="7"/>
+      <c r="G221" s="7"/>
+      <c r="H221" s="7"/>
+      <c r="I221" s="7"/>
+      <c r="J221" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/book_record.xlsx
+++ b/data/book_record.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="519">
   <si>
     <t>title</t>
   </si>
@@ -1556,6 +1556,18 @@
   </si>
   <si>
     <t>Malaysia, Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native Tongue </t>
+  </si>
+  <si>
+    <t>Suzette Haden Elgin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Am Legend </t>
+  </si>
+  <si>
+    <t>Richard Matheson</t>
   </si>
 </sst>
 </file>
@@ -2766,7 +2778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J221"/>
+  <dimension ref="A1:J222"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="47.9688" style="1" customWidth="1"/>
@@ -9466,16 +9478,66 @@
       </c>
     </row>
     <row r="221" ht="13.55" customHeight="1">
-      <c r="A221" s="7"/>
-      <c r="B221" s="7"/>
-      <c r="C221" s="7"/>
-      <c r="D221" s="7"/>
-      <c r="E221" s="7"/>
-      <c r="F221" s="7"/>
-      <c r="G221" s="7"/>
-      <c r="H221" s="7"/>
-      <c r="I221" s="7"/>
-      <c r="J221" s="7"/>
+      <c r="A221" t="s" s="5">
+        <v>515</v>
+      </c>
+      <c r="B221" t="s" s="5">
+        <v>516</v>
+      </c>
+      <c r="C221" t="s" s="5">
+        <v>25</v>
+      </c>
+      <c r="D221" t="s" s="5">
+        <v>71</v>
+      </c>
+      <c r="E221" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F221" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G221" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="H221" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I221" s="6">
+        <v>10</v>
+      </c>
+      <c r="J221" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="222" ht="13.55" customHeight="1">
+      <c r="A222" t="s" s="5">
+        <v>517</v>
+      </c>
+      <c r="B222" t="s" s="5">
+        <v>518</v>
+      </c>
+      <c r="C222" t="s" s="5">
+        <v>25</v>
+      </c>
+      <c r="D222" t="s" s="5">
+        <v>362</v>
+      </c>
+      <c r="E222" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F222" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G222" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="H222" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I222" s="7"/>
+      <c r="J222" s="6">
+        <v>2026</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/book_record.xlsx
+++ b/data/book_record.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="521">
   <si>
     <t>title</t>
   </si>
@@ -1568,6 +1568,12 @@
   </si>
   <si>
     <t>Richard Matheson</t>
+  </si>
+  <si>
+    <t>Artemis</t>
+  </si>
+  <si>
+    <t>Andy Weir</t>
   </si>
 </sst>
 </file>
@@ -2778,7 +2784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J222"/>
+  <dimension ref="A1:J223"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="47.9688" style="1" customWidth="1"/>
@@ -9539,6 +9545,36 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="223" ht="13.55" customHeight="1">
+      <c r="A223" t="s" s="5">
+        <v>519</v>
+      </c>
+      <c r="B223" t="s" s="5">
+        <v>520</v>
+      </c>
+      <c r="C223" t="s" s="5">
+        <v>25</v>
+      </c>
+      <c r="D223" t="s" s="5">
+        <v>71</v>
+      </c>
+      <c r="E223" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F223" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G223" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="H223" t="s" s="5">
+        <v>415</v>
+      </c>
+      <c r="I223" s="7"/>
+      <c r="J223" s="6">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>

--- a/data/book_record.xlsx
+++ b/data/book_record.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="522">
   <si>
     <t>title</t>
   </si>
@@ -1574,6 +1574,9 @@
   </si>
   <si>
     <t>Andy Weir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Perfect Vacuum </t>
   </si>
 </sst>
 </file>
@@ -2784,7 +2787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J223"/>
+  <dimension ref="A1:J224"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="47.9688" style="1" customWidth="1"/>
@@ -9575,6 +9578,36 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="224" ht="13.55" customHeight="1">
+      <c r="A224" t="s" s="5">
+        <v>521</v>
+      </c>
+      <c r="B224" t="s" s="5">
+        <v>375</v>
+      </c>
+      <c r="C224" t="s" s="5">
+        <v>63</v>
+      </c>
+      <c r="D224" t="s" s="5">
+        <v>281</v>
+      </c>
+      <c r="E224" t="s" s="5">
+        <v>27</v>
+      </c>
+      <c r="F224" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G224" t="s" s="5">
+        <v>376</v>
+      </c>
+      <c r="H224" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I224" s="7"/>
+      <c r="J224" s="6">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>

--- a/data/book_record.xlsx
+++ b/data/book_record.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="524">
   <si>
     <t>title</t>
   </si>
@@ -1577,6 +1577,12 @@
   </si>
   <si>
     <t xml:space="preserve">A Perfect Vacuum </t>
+  </si>
+  <si>
+    <t>The Long Tomorrow</t>
+  </si>
+  <si>
+    <t>Leigh Brackett</t>
   </si>
 </sst>
 </file>
@@ -1692,19 +1698,19 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -1876,9 +1882,9 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -1958,7 +1964,7 @@
         </a:effectLst>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1985,10 +1991,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -2235,9 +2241,9 @@
           <a:round/>
         </a:ln>
         <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
             <a:srgbClr val="000000">
-              <a:alpha val="38000"/>
+              <a:alpha val="35000"/>
             </a:srgbClr>
           </a:outerShdw>
         </a:effectLst>
@@ -2515,7 +2521,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -2542,10 +2548,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -2787,18 +2793,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J224"/>
+  <dimension ref="A1:J225"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="47.9688" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5312" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.4141" style="1" customWidth="1"/>
+    <col min="1" max="1" width="48" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="38.8516" style="1" customWidth="1"/>
     <col min="5" max="6" width="8.85156" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.6719" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.3516" style="1" customWidth="1"/>
     <col min="9" max="9" width="5.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.8125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.8516" style="1" customWidth="1"/>
     <col min="11" max="16384" width="8.85156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9605,6 +9611,36 @@
       </c>
       <c r="I224" s="7"/>
       <c r="J224" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="225" ht="13.55" customHeight="1">
+      <c r="A225" t="s" s="5">
+        <v>522</v>
+      </c>
+      <c r="B225" t="s" s="5">
+        <v>523</v>
+      </c>
+      <c r="C225" t="s" s="5">
+        <v>25</v>
+      </c>
+      <c r="D225" t="s" s="5">
+        <v>71</v>
+      </c>
+      <c r="E225" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F225" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G225" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="H225" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I225" s="7"/>
+      <c r="J225" s="6">
         <v>2026</v>
       </c>
     </row>

--- a/data/book_record.xlsx
+++ b/data/book_record.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="527">
   <si>
     <t>title</t>
   </si>
@@ -1583,6 +1583,15 @@
   </si>
   <si>
     <t>Leigh Brackett</t>
+  </si>
+  <si>
+    <t>On the Beach</t>
+  </si>
+  <si>
+    <t>Nevil Shute</t>
+  </si>
+  <si>
+    <t>United Kingdom, Australia</t>
   </si>
 </sst>
 </file>
@@ -2793,7 +2802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J225"/>
+  <dimension ref="A1:J226"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="48" style="1" customWidth="1"/>
@@ -9644,6 +9653,36 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="226" ht="13.55" customHeight="1">
+      <c r="A226" t="s" s="5">
+        <v>524</v>
+      </c>
+      <c r="B226" t="s" s="5">
+        <v>525</v>
+      </c>
+      <c r="C226" t="s" s="5">
+        <v>526</v>
+      </c>
+      <c r="D226" t="s" s="5">
+        <v>367</v>
+      </c>
+      <c r="E226" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="F226" t="s" s="5">
+        <v>48</v>
+      </c>
+      <c r="G226" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="H226" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="I226" s="7"/>
+      <c r="J226" s="6">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
